--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2382-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2382-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A010DD84-37AA-4518-B847-9C8F30934759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EDA87D1-EAF3-4638-A112-78B81A63761C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{710F49DE-E7C6-4891-BBFD-5B81193839EE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{FA649553-F505-45D3-A60F-EE4F0157D113}"/>
   </bookViews>
   <sheets>
     <sheet name="2382-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1463,25 +1463,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBBE0FF-71BF-4144-B2B6-A9748E191756}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90685377-FB7F-47F4-A161-534D96F4B515}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1635,7 +1635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2023</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2022</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2021</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2020</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2019</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2018</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2017</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2016</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2015</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2014</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2013</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2012</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2011</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2010</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2009</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2008</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2007</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2006</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2005</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2004</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2003</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2002</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2001</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2000</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>1999</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>1998</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>1997</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>1996</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>1995</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>1994</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>1993</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40" t="s">
         <v>39</v>
       </c>
